--- a/data/export/2026-10-14-operations.xlsx
+++ b/data/export/2026-10-14-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1583,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1918,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1979,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2023,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2099,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2118,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2154,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2375,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2451,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2470,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2495,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2506,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2519,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2567,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2586,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,25 +2622,25 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2610,41 +2650,37 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2652,7 +2688,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2676,17 +2712,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2696,45 +2732,41 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2772,7 +2804,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2786,7 +2818,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2822,35 +2854,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2888,7 +2920,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2902,7 +2934,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2938,35 +2970,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2999,12 +3031,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3018,7 +3050,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3054,7 +3086,3487 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-operations.xlsx
+++ b/data/export/2026-10-14-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD52"/>
+  <dimension ref="A1:AD79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -891,36 +891,32 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -928,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -952,17 +948,17 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -972,17 +968,13 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1007,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1068,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1088,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1141,24 +1141,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1316,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1379,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1440,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1536,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1559,7 +1575,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1570,7 +1586,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1652,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1675,7 +1691,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1686,7 +1702,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1735,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1752,7 +1772,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1796,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1892,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1918,7 +1942,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2008,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2038,7 +2062,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2128,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2154,7 +2178,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2244,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2270,7 +2294,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2360,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2380,17 +2404,13 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2403,22 +2423,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2456,7 +2476,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2470,7 +2490,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2500,41 +2520,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2567,12 +2591,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2586,7 +2610,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2611,46 +2635,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2683,12 +2711,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2702,7 +2730,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2727,46 +2755,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2799,12 +2831,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2818,7 +2850,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2854,35 +2886,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2915,12 +2947,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2934,7 +2966,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2959,46 +2991,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3031,12 +3067,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3050,7 +3086,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3075,46 +3111,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3147,12 +3187,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3166,7 +3206,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3191,7 +3231,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3202,35 +3242,35 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3263,12 +3303,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3282,7 +3322,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3307,46 +3347,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3379,12 +3423,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3398,7 +3442,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3423,7 +3467,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3434,7 +3478,7 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3447,60 +3491,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3514,7 +3562,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3524,33 +3572,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -3563,60 +3615,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3630,7 +3686,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3640,33 +3696,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -3679,60 +3739,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3746,7 +3810,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3756,17 +3820,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3776,13 +3840,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -3795,22 +3863,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3843,12 +3911,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3862,7 +3930,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3898,7 +3966,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3979,32 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3959,12 +4027,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3972,13 +4040,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4014,7 +4098,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4027,22 +4111,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4075,12 +4159,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4094,7 +4178,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4130,7 +4214,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4143,22 +4227,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4191,12 +4275,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4210,7 +4294,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4246,7 +4330,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4343,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4269,7 +4353,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4307,12 +4391,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4326,7 +4410,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4362,7 +4446,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4459,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4385,7 +4469,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4423,12 +4507,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4442,7 +4526,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4478,7 +4562,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4491,22 +4575,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4539,12 +4623,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4558,7 +4642,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4594,7 +4678,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4607,22 +4691,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4655,12 +4739,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4674,7 +4758,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4710,35 +4794,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4771,12 +4855,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4874,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4815,7 +4899,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4826,35 +4910,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4887,12 +4971,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4906,7 +4990,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4942,35 +5026,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5003,12 +5087,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5022,7 +5106,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5058,35 +5142,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5119,12 +5203,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5138,7 +5222,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5174,35 +5258,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5235,12 +5319,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5254,7 +5338,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5290,35 +5374,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5351,12 +5435,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5370,7 +5454,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5406,35 +5490,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5467,12 +5551,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5486,7 +5570,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5522,35 +5606,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5583,12 +5667,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5602,7 +5686,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5638,35 +5722,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5699,12 +5783,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5718,7 +5802,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5754,35 +5838,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5815,12 +5899,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5834,7 +5918,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5870,35 +5954,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5931,12 +6015,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5950,7 +6034,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5986,35 +6070,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6047,12 +6131,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6066,7 +6150,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6102,35 +6186,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6163,12 +6247,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6182,7 +6266,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6218,35 +6302,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6279,12 +6363,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6298,7 +6382,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6334,35 +6418,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6395,12 +6479,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6414,7 +6498,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6450,35 +6534,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6516,7 +6600,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6530,7 +6614,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6560,13 +6644,3201 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>1/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC52" s="2" t="inlineStr"/>
-      <c r="AD52" s="2" t="inlineStr">
-        <is>
-          <t>—/15</t>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-operations.xlsx
+++ b/data/export/2026-10-14-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD79"/>
+  <dimension ref="A1:AD95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1745,24 +1745,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1975,32 +1975,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2008,7 +2012,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2032,37 +2036,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2095,32 +2099,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2128,7 +2136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2152,33 +2160,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2256,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2360,7 +2372,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2399,7 +2411,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2476,7 +2488,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2530,7 +2542,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2608,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2716,7 +2728,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2770,7 +2782,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2848,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2952,7 +2964,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3006,7 +3018,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3084,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3126,7 +3138,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3204,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3308,7 +3320,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3357,12 +3369,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3440,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3485,70 +3497,66 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3562,7 +3570,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3572,17 +3580,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3592,87 +3600,79 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3696,107 +3696,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3810,7 +3806,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3820,65 +3816,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3911,12 +3907,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3930,7 +3926,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3955,7 +3951,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3966,7 +3962,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3975,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3989,7 +3985,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3999,32 +3995,36 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4040,29 +4040,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq28（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:51</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4072,33 +4056,37 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -4111,60 +4099,64 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4178,7 +4170,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4188,33 +4180,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -4227,52 +4223,56 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4304,33 +4304,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -4343,60 +4347,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4410,7 +4418,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4420,33 +4428,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -4459,32 +4471,32 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4507,12 +4519,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4520,13 +4532,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
-      <c r="U34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4551,7 +4579,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4575,7 +4603,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4585,7 +4613,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4595,40 +4623,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4642,7 +4674,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4652,33 +4684,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4727,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4701,7 +4737,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4711,40 +4747,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4758,7 +4798,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4768,33 +4808,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4851,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4817,7 +4861,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4855,12 +4899,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4874,7 +4918,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4899,7 +4943,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4923,7 +4967,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4933,7 +4977,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4971,12 +5015,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4990,7 +5034,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5039,22 +5083,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5087,12 +5131,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5106,7 +5150,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5155,22 +5199,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5203,12 +5247,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5222,7 +5266,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5271,7 +5315,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5281,7 +5325,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5319,12 +5363,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5338,7 +5382,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5387,7 +5431,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5397,7 +5441,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5435,12 +5479,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5454,7 +5498,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5503,7 +5547,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5513,7 +5557,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5551,12 +5595,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5570,7 +5614,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5619,7 +5663,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5629,7 +5673,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5667,12 +5711,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5686,7 +5730,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5735,7 +5779,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5745,7 +5789,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5788,7 +5832,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5802,7 +5846,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5851,7 +5895,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5861,7 +5905,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5899,12 +5943,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5918,7 +5962,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5967,7 +6011,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5977,7 +6021,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6015,12 +6059,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6034,7 +6078,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6083,7 +6127,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6093,7 +6137,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6131,12 +6175,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6150,7 +6194,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6199,22 +6243,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6247,12 +6291,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6266,7 +6310,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6315,22 +6359,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6368,7 +6412,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6382,7 +6426,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6431,7 +6475,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6441,7 +6485,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6479,12 +6523,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6498,7 +6542,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6547,7 +6591,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6557,7 +6601,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6600,7 +6644,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6614,7 +6658,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6639,22 +6683,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6707,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6677,7 +6717,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6720,7 +6760,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6734,7 +6774,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6759,50 +6799,46 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6840,7 +6876,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6854,7 +6890,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6879,7 +6915,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6890,77 +6926,73 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6974,7 +7006,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6984,65 +7016,61 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7080,7 +7108,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7094,7 +7122,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7124,83 +7152,83 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7214,7 +7242,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7224,17 +7252,17 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7249,40 +7277,40 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7315,12 +7343,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7334,7 +7362,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7364,83 +7392,83 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7454,7 +7482,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7464,17 +7492,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7489,82 +7517,78 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7578,7 +7602,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7588,17 +7612,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7608,45 +7632,41 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7679,12 +7699,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7698,7 +7718,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7723,46 +7743,50 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7795,12 +7819,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7814,7 +7838,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7839,46 +7863,50 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7911,12 +7939,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7930,7 +7958,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7966,7 +7994,7 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -7979,7 +8007,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -7989,7 +8017,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8027,12 +8055,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8046,7 +8074,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8071,7 +8099,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8095,60 +8123,64 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8162,7 +8194,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8172,33 +8204,37 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8247,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8221,7 +8257,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8259,12 +8295,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8278,7 +8314,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8303,7 +8339,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8327,60 +8363,64 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8394,7 +8434,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8404,33 +8444,37 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8443,60 +8487,64 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8510,7 +8558,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8520,33 +8568,37 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8559,52 +8611,56 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8612,7 +8668,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8626,7 +8682,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8636,33 +8692,37 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8735,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8685,7 +8745,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8695,40 +8755,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8742,7 +8806,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8752,17 +8816,17 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8772,13 +8836,17 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8859,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8801,7 +8869,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8839,12 +8907,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8858,7 +8926,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8883,7 +8951,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8907,60 +8975,64 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:09</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8974,7 +9046,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8984,17 +9056,17 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9009,12 +9081,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9027,60 +9099,64 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9094,7 +9170,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9104,17 +9180,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9129,12 +9205,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9147,60 +9223,64 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9214,7 +9294,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9224,33 +9304,37 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9263,60 +9347,64 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9330,7 +9418,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9340,17 +9428,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9365,12 +9453,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9383,22 +9471,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9431,12 +9519,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9450,7 +9538,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9499,7 +9587,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9509,7 +9597,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9547,12 +9635,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9566,7 +9654,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9591,22 +9679,18 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9619,7 +9703,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9629,7 +9713,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9639,40 +9723,44 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9686,7 +9774,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9696,17 +9784,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9716,13 +9804,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9827,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9745,7 +9837,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9783,12 +9875,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9802,7 +9894,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9827,7 +9919,7 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9839,6 +9931,1902 @@
       <c r="AD79" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-operations.xlsx
+++ b/data/export/2026-10-14-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD95"/>
+  <dimension ref="A1:AD102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -968,13 +968,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1083,22 +1087,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1222,7 +1226,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1416,7 +1420,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1536,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1652,7 +1656,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1772,7 +1776,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1826,7 +1830,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1896,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2012,7 +2016,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2136,7 +2140,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2223,32 +2227,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2256,7 +2264,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2280,33 +2288,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2339,32 +2351,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2372,7 +2388,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2396,17 +2412,17 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2416,13 +2432,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2455,32 +2475,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2488,7 +2512,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2512,17 +2536,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2532,17 +2556,17 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2575,32 +2599,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2608,7 +2636,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2632,37 +2660,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2756,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2782,7 +2810,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2876,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2964,7 +2992,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3084,7 +3112,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3204,7 +3232,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3320,7 +3348,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3374,7 +3402,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3468,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3556,7 +3584,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3672,7 +3700,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3792,7 +3820,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3859,22 +3887,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3907,12 +3935,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3951,88 +3979,88 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4046,7 +4074,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4056,22 +4084,22 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4081,82 +4109,78 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4170,7 +4194,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4180,37 +4204,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4247,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4233,7 +4257,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4253,24 +4277,24 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4280,7 +4304,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4294,7 +4318,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4329,12 +4353,12 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4371,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4357,7 +4381,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4377,12 +4401,12 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
@@ -4404,7 +4428,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4418,7 +4442,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4453,7 +4477,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -4471,7 +4495,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4481,7 +4505,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4491,32 +4515,36 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4524,7 +4552,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4532,29 +4560,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>物理seq28（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>07:51</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4564,17 +4576,17 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4584,13 +4596,17 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -4603,24 +4619,24 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4633,12 +4649,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
@@ -4655,12 +4671,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4674,7 +4690,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4709,7 +4725,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4727,56 +4743,52 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4784,7 +4796,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4792,13 +4804,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4808,17 +4836,17 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4828,17 +4856,13 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4875,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4861,7 +4885,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4871,40 +4895,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4918,7 +4946,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4928,17 +4956,17 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4948,13 +4976,17 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4999,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4977,7 +5009,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4987,40 +5019,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5034,7 +5070,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5044,33 +5080,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5123,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5093,7 +5133,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5103,32 +5143,36 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5136,7 +5180,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5150,7 +5194,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5160,33 +5204,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5247,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5209,7 +5257,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5247,12 +5295,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5266,7 +5314,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5291,7 +5339,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5315,7 +5363,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5325,7 +5373,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5363,12 +5411,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5382,7 +5430,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5407,7 +5455,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5431,7 +5479,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5441,7 +5489,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5479,12 +5527,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5498,7 +5546,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5547,22 +5595,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5595,12 +5643,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5614,7 +5662,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5663,22 +5711,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5711,12 +5759,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5730,7 +5778,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5779,22 +5827,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5827,12 +5875,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5846,7 +5894,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5895,22 +5943,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5943,12 +5991,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5962,7 +6010,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6011,22 +6059,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6059,12 +6107,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6078,7 +6126,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6127,22 +6175,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6175,12 +6223,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6194,7 +6242,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6243,22 +6291,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6291,12 +6339,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6310,7 +6358,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6359,22 +6407,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6407,12 +6455,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6426,7 +6474,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6475,22 +6523,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6523,12 +6571,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6542,7 +6590,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6591,22 +6639,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6644,7 +6692,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6658,7 +6706,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6707,7 +6755,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6717,7 +6765,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6755,12 +6803,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6774,7 +6822,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6823,7 +6871,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6833,7 +6881,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6876,7 +6924,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6890,7 +6938,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6939,7 +6987,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6949,7 +6997,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6987,12 +7035,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7006,7 +7054,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7055,7 +7103,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7065,7 +7113,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7108,7 +7156,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7122,7 +7170,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7147,22 +7195,18 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -7175,7 +7219,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7185,7 +7229,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7223,12 +7267,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7242,7 +7286,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7267,22 +7311,18 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7335,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7305,7 +7345,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7348,7 +7388,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7362,7 +7402,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7397,7 +7437,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
@@ -7415,7 +7455,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7425,7 +7465,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7468,7 +7508,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7482,7 +7522,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7517,12 +7557,12 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7575,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7545,7 +7585,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7588,7 +7628,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7602,7 +7642,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7632,13 +7672,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7695,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7661,7 +7705,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7699,12 +7743,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7718,7 +7762,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7753,12 +7797,12 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7815,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7781,7 +7825,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7824,7 +7868,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7838,7 +7882,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7868,17 +7912,13 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7931,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7901,7 +7941,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7939,12 +7979,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7958,7 +7998,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7988,41 +8028,45 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8060,7 +8104,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8074,7 +8118,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8104,83 +8148,83 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8194,7 +8238,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8204,17 +8248,17 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8229,40 +8273,40 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8295,12 +8339,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8314,7 +8358,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8350,77 +8394,73 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8434,7 +8474,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8444,17 +8484,17 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8464,17 +8504,13 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8523,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8497,7 +8533,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8507,44 +8543,40 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>114分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8558,7 +8590,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8568,17 +8600,17 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8588,17 +8620,13 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8611,24 +8639,24 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8641,12 +8669,12 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
@@ -8663,12 +8691,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8682,7 +8710,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8707,7 +8735,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8717,12 +8745,12 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8735,64 +8763,60 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8806,7 +8830,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8816,37 +8840,33 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8859,52 +8879,56 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8912,7 +8936,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8926,7 +8950,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8936,17 +8960,17 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8956,13 +8980,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8975,7 +9003,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8985,7 +9013,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9005,12 +9033,12 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
@@ -9027,12 +9055,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9046,7 +9074,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9081,12 +9109,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9127,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9109,7 +9137,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9129,34 +9157,34 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9170,7 +9198,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9205,12 +9233,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9223,24 +9251,24 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9253,34 +9281,34 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>110分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9294,7 +9322,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9329,12 +9357,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9347,64 +9375,60 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9418,7 +9442,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9428,17 +9452,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9448,17 +9472,13 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9491,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9481,7 +9501,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9491,40 +9511,44 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9538,7 +9562,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9548,17 +9572,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9568,13 +9592,17 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9587,60 +9615,64 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9654,7 +9686,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9664,33 +9696,37 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9703,24 +9739,24 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9733,34 +9769,34 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9774,7 +9810,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9809,12 +9845,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9827,60 +9863,64 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9894,7 +9934,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9904,33 +9944,37 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9943,60 +9987,64 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10010,7 +10058,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10020,17 +10068,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10040,13 +10088,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC80" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10111,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -10069,7 +10121,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -10079,40 +10131,44 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10126,7 +10182,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10136,17 +10192,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10156,13 +10212,17 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC81" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10235,7 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -10185,7 +10245,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10195,32 +10255,36 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10228,7 +10292,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10242,7 +10306,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10252,17 +10316,17 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10277,7 +10341,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
@@ -10295,7 +10359,7 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -10305,7 +10369,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10348,7 +10412,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10362,7 +10426,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10392,17 +10456,13 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC83" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10475,7 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -10425,7 +10485,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10463,12 +10523,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10482,7 +10542,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10507,7 +10567,7 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
@@ -10531,7 +10591,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10541,7 +10601,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10579,12 +10639,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10598,7 +10658,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10623,22 +10683,18 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC85" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10707,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10661,7 +10717,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10704,7 +10760,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10718,7 +10774,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10743,18 +10799,22 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC86" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10767,7 +10827,7 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -10777,7 +10837,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -10820,7 +10880,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10834,7 +10894,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10869,12 +10929,12 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10947,7 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -10897,7 +10957,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -10935,12 +10995,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10954,7 +11014,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -10979,22 +11039,18 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC88" s="2" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11007,22 +11063,22 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -11060,7 +11116,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11074,7 +11130,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11104,13 +11160,17 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11123,22 +11183,22 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -11171,12 +11231,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11190,7 +11250,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11215,22 +11275,18 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC90" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11243,22 +11299,22 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -11291,12 +11347,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11310,7 +11366,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11345,12 +11401,12 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11363,22 +11419,22 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -11411,12 +11467,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11430,7 +11486,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11465,12 +11521,12 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11483,7 +11539,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11493,7 +11549,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11531,12 +11587,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11550,7 +11606,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11580,17 +11636,13 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11603,22 +11655,22 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -11651,12 +11703,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11670,7 +11722,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11700,13 +11752,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11719,22 +11775,22 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11767,12 +11823,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11786,47 +11842,879 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="W95" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X95" s="2" t="inlineStr">
+      <c r="X98" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y95" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z95" s="2" t="inlineStr">
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA95" s="2" t="inlineStr">
+      <c r="AA98" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB95" s="2" t="inlineStr">
+      <c r="AB98" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC95" s="2" t="inlineStr">
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="AD95" s="2" t="inlineStr">
-        <is>
-          <t>6/18</t>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-operations.xlsx
+++ b/data/export/2026-10-14-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -968,17 +968,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2444,17 +2444,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4792,17 +4792,17 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5404,12 +5404,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5528,17 +5528,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6153,12 +6153,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7880,17 +7880,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8128,17 +8128,17 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9236,17 +9236,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10228,12 +10228,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10724,12 +10724,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10968,17 +10968,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11503,32 +11503,36 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11536,7 +11540,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11560,17 +11564,17 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11580,12 +11584,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11633,12 +11637,12 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
@@ -11660,7 +11664,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11709,12 +11713,12 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11747,32 +11751,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11780,7 +11788,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11804,17 +11812,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11824,12 +11832,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
@@ -11867,32 +11875,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11900,7 +11912,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11924,17 +11936,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11944,12 +11956,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
@@ -11987,32 +11999,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12020,7 +12036,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12044,17 +12060,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12064,17 +12080,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -12107,32 +12123,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12140,7 +12160,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12164,17 +12184,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12184,17 +12204,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -12260,7 +12280,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12309,12 +12329,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12400,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12424,12 +12444,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
@@ -12504,7 +12524,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12548,17 +12568,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -12806,7 +12826,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12930,7 +12950,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13152,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13186,7 +13206,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -13256,7 +13276,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13305,12 +13325,12 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -13434,7 +13454,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13578,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -13628,7 +13648,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13682,7 +13702,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13772,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13796,17 +13816,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -13992,7 +14012,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14036,17 +14056,17 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -14166,7 +14186,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14252,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14286,7 +14306,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -14410,7 +14430,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -14480,7 +14500,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14524,17 +14544,17 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -14604,7 +14624,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14658,7 +14678,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14748,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14772,17 +14792,17 @@
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -14968,7 +14988,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15012,17 +15032,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -15092,7 +15112,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15146,7 +15166,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15290,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -15340,7 +15360,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15384,17 +15404,17 @@
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC121" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -15588,7 +15608,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15642,7 +15662,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -15832,7 +15852,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15876,17 +15896,17 @@
       </c>
       <c r="AB125" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16026,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16150,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -16332,7 +16352,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16386,7 +16406,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -16456,7 +16476,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16505,12 +16525,12 @@
       </c>
       <c r="AC130" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16654,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16778,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16848,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16882,7 +16902,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -16952,7 +16972,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -16996,17 +17016,17 @@
       </c>
       <c r="AB134" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC134" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17096,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17120,17 +17140,17 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17398,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -17448,7 +17468,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17502,7 +17522,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -17572,7 +17592,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17616,17 +17636,17 @@
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -17750,7 +17770,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -17820,7 +17840,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17874,7 +17894,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17964,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -17988,17 +18008,17 @@
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -18064,7 +18084,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18118,7 +18138,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -18312,7 +18332,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18366,7 +18386,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -18614,7 +18634,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -18738,7 +18758,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -18862,7 +18882,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -18928,7 +18948,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19118,7 +19138,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -19490,7 +19510,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -19560,7 +19580,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19808,7 +19828,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19862,7 +19882,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -20110,7 +20130,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -20234,7 +20254,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -20482,7 +20502,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -20552,7 +20572,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20601,12 +20621,12 @@
       </c>
       <c r="AC163" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -20928,7 +20948,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -20972,17 +20992,17 @@
       </c>
       <c r="AB166" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC166" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21068,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21168,7 +21188,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21212,17 +21232,17 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -21292,7 +21312,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21336,17 +21356,17 @@
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -21416,7 +21436,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21460,17 +21480,17 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -21540,7 +21560,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21660,7 +21680,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21704,17 +21724,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -21784,7 +21804,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21828,17 +21848,17 @@
       </c>
       <c r="AB173" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -21908,7 +21928,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21962,7 +21982,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22052,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22086,7 +22106,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -22156,7 +22176,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22210,7 +22230,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22354,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -22404,7 +22424,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22458,7 +22478,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22602,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -22706,7 +22726,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -22776,7 +22796,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22830,7 +22850,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -23078,7 +23098,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -23369,24 +23389,24 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O186" s="2" t="inlineStr">
@@ -23396,7 +23416,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23445,12 +23465,12 @@
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -23603,32 +23623,36 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N188" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23636,7 +23660,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23660,17 +23684,17 @@
       </c>
       <c r="X188" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z188" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA188" s="2" t="inlineStr">
@@ -23680,17 +23704,17 @@
       </c>
       <c r="AB188" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC188" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -23723,32 +23747,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23756,7 +23784,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23780,17 +23808,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23800,17 +23828,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -23843,32 +23871,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23876,7 +23908,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23900,17 +23932,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23920,17 +23952,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -23963,32 +23995,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -23996,7 +24032,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24020,17 +24056,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24040,17 +24076,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -24083,12 +24119,12 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -24116,7 +24152,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24124,10 +24160,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R192" s="2" t="inlineStr"/>
-      <c r="S192" s="2" t="inlineStr"/>
-      <c r="T192" s="2" t="inlineStr"/>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 13分钟参与校验</t>
+        </is>
+      </c>
       <c r="V192" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24170,7 +24222,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -24203,32 +24255,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24236,7 +24292,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24260,17 +24316,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24280,17 +24336,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -24323,32 +24379,36 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -24356,7 +24416,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24380,17 +24440,17 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA194" s="2" t="inlineStr">
@@ -24400,17 +24460,17 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -24476,7 +24536,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24563,12 +24623,12 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -24596,7 +24656,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24604,10 +24664,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R196" s="2" t="inlineStr"/>
-      <c r="S196" s="2" t="inlineStr"/>
-      <c r="T196" s="2" t="inlineStr"/>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V196" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24650,7 +24726,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24792,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24770,7 +24846,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -24803,32 +24879,36 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -24836,7 +24916,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24860,17 +24940,17 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA198" s="2" t="inlineStr">
@@ -24880,17 +24960,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -24956,7 +25036,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25010,7 +25090,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -25076,7 +25156,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25130,7 +25210,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -25196,7 +25276,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25250,7 +25330,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -25316,7 +25396,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25360,17 +25440,17 @@
       </c>
       <c r="AB202" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -25436,7 +25516,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25480,17 +25560,17 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -25928,7 +26008,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -25977,12 +26057,12 @@
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26132,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26096,12 +26176,12 @@
       </c>
       <c r="AB208" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
@@ -26350,7 +26430,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -26420,7 +26500,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26464,17 +26544,17 @@
       </c>
       <c r="AB211" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26544,7 +26624,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26588,12 +26668,12 @@
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
@@ -26792,7 +26872,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26841,12 +26921,12 @@
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -27218,7 +27298,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -27338,7 +27418,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -27408,7 +27488,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27452,17 +27532,17 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -27958,7 +28038,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -28028,7 +28108,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28072,12 +28152,12 @@
       </c>
       <c r="AB224" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
@@ -28396,7 +28476,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28445,12 +28525,12 @@
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -28574,7 +28654,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -28644,7 +28724,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28688,12 +28768,12 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
@@ -28768,7 +28848,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28812,17 +28892,17 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28892,7 +28972,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28941,12 +29021,12 @@
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -29318,7 +29398,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -29442,7 +29522,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -29880,7 +29960,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -29936,12 +30016,12 @@
       </c>
       <c r="AB239" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
@@ -30194,7 +30274,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -30260,7 +30340,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30316,12 +30396,12 @@
       </c>
       <c r="AB242" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC242" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AD242" s="2" t="inlineStr">
@@ -30396,7 +30476,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30445,12 +30525,12 @@
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -30698,7 +30778,7 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -31442,7 +31522,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -31512,7 +31592,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31561,12 +31641,12 @@
       </c>
       <c r="AC252" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31894,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -32504,7 +32584,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32548,17 +32628,17 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -32682,7 +32762,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -32752,7 +32832,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32801,12 +32881,12 @@
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -33000,7 +33080,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33049,12 +33129,12 @@
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -33364,7 +33444,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33408,17 +33488,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -33542,7 +33622,7 @@
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -33736,7 +33816,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33780,12 +33860,12 @@
       </c>
       <c r="AB270" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
@@ -34108,7 +34188,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34152,12 +34232,12 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
@@ -34476,7 +34556,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34520,17 +34600,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -34654,7 +34734,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -35146,7 +35226,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -35216,7 +35296,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35265,12 +35345,12 @@
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -35340,7 +35420,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35389,12 +35469,12 @@
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -35464,7 +35544,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35508,17 +35588,17 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -35584,7 +35664,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35628,12 +35708,12 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -36080,7 +36160,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36124,12 +36204,12 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
@@ -36576,7 +36656,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36620,17 +36700,17 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -36921,24 +37001,24 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr"/>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N296" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O296" s="2" t="inlineStr">
@@ -36948,7 +37028,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -36997,12 +37077,12 @@
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -37045,24 +37125,24 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr"/>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N297" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O297" s="2" t="inlineStr">
@@ -37072,7 +37152,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37121,12 +37201,12 @@
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -37159,32 +37239,36 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr"/>
       <c r="M298" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N298" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O298" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -37192,7 +37276,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37216,17 +37300,17 @@
       </c>
       <c r="X298" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z298" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA298" s="2" t="inlineStr">
@@ -37236,12 +37320,12 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
@@ -37279,32 +37363,36 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr"/>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N299" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N299" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O299" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37312,7 +37400,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37336,17 +37424,17 @@
       </c>
       <c r="X299" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z299" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA299" s="2" t="inlineStr">
@@ -37356,17 +37444,17 @@
       </c>
       <c r="AB299" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -37399,32 +37487,36 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr"/>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N300" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O300" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37432,7 +37524,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37456,17 +37548,17 @@
       </c>
       <c r="X300" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z300" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA300" s="2" t="inlineStr">
@@ -37476,12 +37568,12 @@
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
@@ -37519,32 +37611,36 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N301" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O301" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -37552,7 +37648,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37576,17 +37672,17 @@
       </c>
       <c r="X301" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z301" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA301" s="2" t="inlineStr">
@@ -37596,17 +37692,17 @@
       </c>
       <c r="AB301" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -37672,7 +37768,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37721,12 +37817,12 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -37792,7 +37888,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37836,17 +37932,17 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-operations.xlsx
+++ b/data/export/2026-10-14-operations.xlsx
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3924,17 +3924,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5160,17 +5160,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5404,17 +5404,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6148,17 +6148,17 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6396,17 +6396,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8620,17 +8620,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8740,17 +8740,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10104,17 +10104,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10228,17 +10228,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11341,12 +11341,12 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11708,17 +11708,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11912,7 +11912,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11956,17 +11956,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -12133,12 +12133,12 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -12247,32 +12247,36 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -12280,7 +12284,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12304,17 +12308,17 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -12324,17 +12328,17 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -12367,32 +12371,36 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -12400,7 +12408,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12424,17 +12432,17 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
@@ -12444,17 +12452,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -12578,7 +12586,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -12826,7 +12834,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12950,7 +12958,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13160,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13196,17 +13204,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13338,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -13454,7 +13462,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -13578,7 +13586,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -13648,7 +13656,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13692,17 +13700,17 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13834,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13954,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -14066,7 +14074,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -14186,7 +14194,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14260,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14296,17 +14304,17 @@
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC112" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -14430,7 +14438,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14508,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14549,12 +14557,12 @@
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -14624,7 +14632,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14668,17 +14676,17 @@
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -14748,7 +14756,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14922,7 +14930,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -15042,7 +15050,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15298,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -15414,7 +15422,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15546,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15616,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15662,7 +15670,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -15906,7 +15914,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -16026,7 +16034,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16158,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -16352,7 +16360,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16396,17 +16404,17 @@
       </c>
       <c r="AB129" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC129" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -16530,7 +16538,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -16654,7 +16662,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -16778,7 +16786,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -16848,7 +16856,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16892,17 +16900,17 @@
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC133" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17034,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -17150,7 +17158,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17282,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -17398,7 +17406,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -17468,7 +17476,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17512,17 +17520,17 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -17592,7 +17600,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17641,12 +17649,12 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -17770,7 +17778,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -17840,7 +17848,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17884,17 +17892,17 @@
       </c>
       <c r="AB141" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -17964,7 +17972,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18262,7 +18270,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -18332,7 +18340,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18386,7 +18394,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -18510,7 +18518,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18642,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -18758,7 +18766,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -18882,7 +18890,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -19138,7 +19146,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -19262,7 +19270,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -19510,7 +19518,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -19758,7 +19766,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -19828,7 +19836,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19872,17 +19880,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20014,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -20130,7 +20138,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -20254,7 +20262,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -20502,7 +20510,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -20626,7 +20634,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -21002,7 +21010,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -21242,7 +21250,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21374,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21498,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -21680,7 +21688,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21729,12 +21737,12 @@
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -21858,7 +21866,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -22052,7 +22060,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22096,17 +22104,17 @@
       </c>
       <c r="AB175" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -22176,7 +22184,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22230,7 +22238,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -22354,7 +22362,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -22424,7 +22432,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22468,17 +22476,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -22602,7 +22610,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -22726,7 +22734,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -22796,7 +22804,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22840,17 +22848,17 @@
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -22974,7 +22982,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -23098,7 +23106,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -23346,7 +23354,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -23470,7 +23478,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -23660,7 +23668,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23838,7 +23846,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -23962,7 +23970,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -24086,7 +24094,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -24346,7 +24354,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -24470,7 +24478,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -24628,7 +24636,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -24656,7 +24664,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24726,7 +24734,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -24759,32 +24767,36 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -24792,7 +24804,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24816,17 +24828,17 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA197" s="2" t="inlineStr">
@@ -24836,17 +24848,17 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -24889,24 +24901,24 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O198" s="2" t="inlineStr">
@@ -24916,7 +24928,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24965,12 +24977,12 @@
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -25003,32 +25015,36 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N199" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -25036,7 +25052,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25060,17 +25076,17 @@
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA199" s="2" t="inlineStr">
@@ -25080,17 +25096,17 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -25123,32 +25139,36 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -25156,7 +25176,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25180,17 +25200,17 @@
       </c>
       <c r="X200" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z200" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA200" s="2" t="inlineStr">
@@ -25200,17 +25220,17 @@
       </c>
       <c r="AB200" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -25243,32 +25263,36 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N201" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -25276,7 +25300,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25300,17 +25324,17 @@
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA201" s="2" t="inlineStr">
@@ -25320,17 +25344,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25420,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25516,7 +25540,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -26008,7 +26032,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26052,12 +26076,12 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
@@ -26500,7 +26524,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -27488,7 +27512,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -28476,7 +28500,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28520,12 +28544,12 @@
       </c>
       <c r="AB227" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
@@ -28848,7 +28872,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -32584,7 +32608,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -33080,7 +33104,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33124,12 +33148,12 @@
       </c>
       <c r="AB264" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
@@ -33444,7 +33468,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -34556,7 +34580,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -35296,7 +35320,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35340,12 +35364,12 @@
       </c>
       <c r="AB282" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
@@ -35544,7 +35568,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -36656,7 +36680,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -37152,7 +37176,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37196,12 +37220,12 @@
       </c>
       <c r="AB297" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
@@ -37400,7 +37424,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37648,7 +37672,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37735,32 +37759,36 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N302" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O302" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -37768,7 +37796,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37792,17 +37820,17 @@
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA302" s="2" t="inlineStr">
@@ -37812,12 +37840,12 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
@@ -37888,7 +37916,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
